--- a/processed_ruby_restored_xlsx/sc248_みるくＡ：遊園地.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc248_みるくＡ：遊園地.ss.xlsx
@@ -1154,8 +1154,9 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>At first, when everyone started going around, she did,
-but now she's looking around much more cautiously.</t>
+          <t>At first, when everyone started going around, she
+did, but now she's looking around much more
+cautiously.</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1185,8 +1186,8 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>「Ah...we saw the Ferris wheel earlier, how about going
-on that？」</t>
+          <t>「Ah...we saw the Ferris wheel earlier, how about
+going on that？」</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1247,9 +1248,9 @@
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>...I expected her to get more excited and shout 'let's
-do back-to-back roller coasters！' or something, so
-this is a bit of a letdown.</t>
+          <t>...I expected her to get more excited and shout
+'let's do back-to-back roller coasters！' or
+something, so this is a bit of a letdown.</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1480,8 +1481,8 @@
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>「S-Stop it！ Onii-chan, you pervert！ There's no way I'd
-do something like that...！」</t>
+          <t>「S-Stop it！ Onii-chan, you pervert！ There's no way
+I'd do something like that...！」</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1633,8 +1634,8 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>Luckily the Ferris wheel wasn’t busy, so our turn came
-up fast.</t>
+          <t>Luckily the Ferris wheel wasn’t busy, so our turn
+came up fast.</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1848,8 +1849,8 @@
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>I deliberately suppressed the excitement inside me and
-said.</t>
+          <t>I deliberately suppressed the excitement inside me
+and said.</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -2002,8 +2003,8 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>My excitement slipped out in the most honest words and
-I ended up getting scolded by Miru-chan...！</t>
+          <t>My excitement slipped out in the most honest words
+and I ended up getting scolded by Miru-chan...！</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2339,8 +2340,8 @@
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>…The legend I just told was something I made up on the
-spot, but she must've believed it honestly.</t>
+          <t>…The legend I just told was something I made up on
+the spot, but she must've believed it honestly.</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2370,8 +2371,8 @@
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>「...！？ Just now, that woman over there flashed a peace
-sign！ Did you see？ Did you see！？」</t>
+          <t>「...！？ Just now, that woman over there flashed a
+peace sign！ Did you see？ Did you see！？」</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2705,7 +2706,8 @@
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>「n, Onii-chan... chu, chuu... chuu！ nngh... nhfuu...！」</t>
+          <t>「n, Onii-chan... chu, chuu... chuu！ nngh...
+nhfuu...！」</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2875,8 +2877,8 @@
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>Touching wasn't enough anymore, and I ended up licking
-Miru-chan's soft lips with my rough tongue.</t>
+          <t>Touching wasn't enough anymore, and I ended up
+licking Miru-chan's soft lips with my rough tongue.</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -3029,8 +3031,8 @@
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>Actually I had been holding my breath too, but I’m too
-embarrassed to say that.</t>
+          <t>Actually I had been holding my breath too, but I’m
+too embarrassed to say that.</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -3075,7 +3077,8 @@
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>「Nn... nnn...！ Chu, nn... smooch！ Chu, pff... pff...！」</t>
+          <t>「Nn... nnn...！ Chu, nn... smooch！ Chu, pff...
+pff...！」</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -3228,7 +3231,8 @@
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>Even the breaths we exhale in between are so erotic...</t>
+          <t>Even the breaths we exhale in between are so
+erotic...</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -3304,8 +3308,8 @@
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>With the tips of our tongues touching, I get the dizzy
-illusion that my tongue might melt away...</t>
+          <t>With the tips of our tongues touching, I get the
+dizzy illusion that my tongue might melt away...</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3395,8 +3399,8 @@
       </c>
       <c r="B192" s="1" t="inlineStr">
         <is>
-          <t>「Faaah... Onii-chan, you're so naughty... chupu, chuu,
-chu... fuu, fuu, fuu...」</t>
+          <t>「Faaah... Onii-chan, you're so naughty... chupu,
+chuu, chu... fuu, fuu, fuu...」</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -3579,8 +3583,8 @@
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t>The wet sounds are so thick they echo as their tongues
-intertwine.</t>
+          <t>The wet sounds are so thick they echo as their
+tongues intertwine.</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3595,8 +3599,8 @@
       </c>
       <c r="B205" s="1" t="inlineStr">
         <is>
-          <t>When that echoes in my head, I somehow get kind of all
-fuzzy and out of it.</t>
+          <t>When that echoes in my head, I somehow get kind of
+all fuzzy and out of it.</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3689,8 +3693,8 @@
       <c r="B211" s="1" t="inlineStr">
         <is>
           <t>When Miru-chan's soft, syrupy saliva slips into my
-mouth, a rush of affection swells up all at once and I
-feel completely filled.</t>
+mouth, a rush of affection swells up all at once and
+I feel completely filled.</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3935,8 +3939,8 @@
       </c>
       <c r="B227" s="1" t="inlineStr">
         <is>
-          <t>Thinking that makes it unstoppable… and because I know
-that, it won't stop me any less！</t>
+          <t>Thinking that makes it unstoppable… and because I
+know that, it won't stop me any less！</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -4133,7 +4137,8 @@
       </c>
       <c r="B240" s="1" t="inlineStr">
         <is>
-          <t>…Miru-chan shook her head no and pulled her lips away.</t>
+          <t>…Miru-chan shook her head no and pulled her lips
+away.</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -4731,7 +4736,8 @@
       </c>
       <c r="B279" s="1" t="inlineStr">
         <is>
-          <t>I smile back at Miru-chan, who asks me as if startled.</t>
+          <t>I smile back at Miru-chan, who asks me as if
+startled.</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -5348,8 +5354,8 @@
       </c>
       <c r="B319" s="1" t="inlineStr">
         <is>
-          <t>When I traced my finger along the slit, a sultry sound
-escaped from Miru-chan’s mouth.</t>
+          <t>When I traced my finger along the slit, a sultry
+sound escaped from Miru-chan’s mouth.</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -6220,8 +6226,8 @@
       <c r="B376" s="1" t="inlineStr">
         <is>
           <t>...Even though it had just been inserted, Miru-chan's
-body twitched uncontrollably from her hips down to her
-legs.</t>
+body twitched uncontrollably from her hips down to
+her legs.</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -6236,8 +6242,8 @@
       </c>
       <c r="B377" s="1" t="inlineStr">
         <is>
-          <t>If my penis isn't holding me up, my hips will sink and
-I'll slide right off.</t>
+          <t>If my penis isn't holding me up, my hips will sink
+and I'll slide right off.</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -6602,8 +6608,8 @@
       </c>
       <c r="B401" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan, looking at me out of the corner of her eye,
-couldn't hold back and begged.</t>
+          <t>Miru-chan, looking at me out of the corner of her
+eye, couldn't hold back and begged.</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -6710,8 +6716,9 @@
       </c>
       <c r="B408" s="1" t="inlineStr">
         <is>
-          <t>I thought I might be stupid too, but teasing her right
-up to the limit might actually have been for the best.</t>
+          <t>I thought I might be stupid too, but teasing her
+right up to the limit might actually have been for
+the best.</t>
         </is>
       </c>
       <c r="C408" t="n">
@@ -6771,7 +6778,8 @@
       </c>
       <c r="B412" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan can't hide her arousal and cries out loudly.</t>
+          <t>Miru-chan can't hide her arousal and cries out
+loudly.</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -6953,7 +6961,8 @@
       </c>
       <c r="B424" s="1" t="inlineStr">
         <is>
-          <t>Your breathing's all labored now, like an excited cow.</t>
+          <t>Your breathing's all labored now, like an excited
+cow.</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -7075,8 +7084,8 @@
       </c>
       <c r="B432" s="1" t="inlineStr">
         <is>
-          <t>「Nn, muuu... faaah... Onii-chan, after all, I can't...
-hold it... anymore...！」</t>
+          <t>「Nn, muuu... faaah... Onii-chan, after all, I
+can't... hold it... anymore...！」</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -7262,7 +7271,8 @@
       </c>
       <c r="B444" s="1" t="inlineStr">
         <is>
-          <t>「Nn, nnn~！ I can… I ca, nna！ Hah！ Haa… fu, faaa… nn~！」</t>
+          <t>「Nn, nnn~！ I can… I ca, nna！ Hah！ Haa… fu, faaa…
+nn~！」</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -7357,8 +7367,9 @@
       <c r="B450" s="1" t="inlineStr">
         <is>
           <t>You don't even have to say anything—Miru-chan's
-arousal rockets higher and higher, and her plentifully
-secreted love juices coat and mingle with me.</t>
+arousal rockets higher and higher, and her
+plentifully secreted love juices coat and mingle with
+me.</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -7558,8 +7569,8 @@
       <c r="B463" s="1" t="inlineStr">
         <is>
           <t>When she says something different from what I was
-thinking, it makes her even more endearing and I start
-to find her really lovable.</t>
+thinking, it makes her even more endearing and I
+start to find her really lovable.</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -7589,8 +7600,8 @@
       </c>
       <c r="B465" s="1" t="inlineStr">
         <is>
-          <t>「Huff... hnn... Your naughty juices are dripping, drip
-drip.」</t>
+          <t>「Huff... hnn... Your naughty juices are dripping,
+drip drip.」</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -7791,8 +7802,8 @@
       </c>
       <c r="B478" s="1" t="inlineStr">
         <is>
-          <t>Her pussy is getting hotter and hotter, and her juices
-leak out like she's wetting herself.</t>
+          <t>Her pussy is getting hotter and hotter, and her
+juices leak out like she's wetting herself.</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -7823,9 +7834,9 @@
       </c>
       <c r="B480" s="1" t="inlineStr">
         <is>
-          <t>The sounds she thinks she's suppressing spill out full
-force; if she holds one thing back, the other can't
-help but give in.</t>
+          <t>The sounds she thinks she's suppressing spill out
+full force; if she holds one thing back, the other
+can't help but give in.</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -7901,8 +7912,8 @@
       </c>
       <c r="B485" s="1" t="inlineStr">
         <is>
-          <t>While watching and thinking about how Miru-chan feels,
-I realized something critical.</t>
+          <t>While watching and thinking about how Miru-chan
+feels, I realized something critical.</t>
         </is>
       </c>
       <c r="C485" t="n">
@@ -8269,8 +8280,9 @@
       </c>
       <c r="B509" s="1" t="inlineStr">
         <is>
-          <t>I panicked, in a different way than before, and seized
-the moment to thrust my hips up as hard as I could.</t>
+          <t>I panicked, in a different way than before, and
+seized the moment to thrust my hips up as hard as I
+could.</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -8488,8 +8500,8 @@
       </c>
       <c r="B523" s="1" t="inlineStr">
         <is>
-          <t>Knowing it was mean, I teased her shame, and it seemed
-something inside Miru-chan burst.</t>
+          <t>Knowing it was mean, I teased her shame, and it
+seemed something inside Miru-chan burst.</t>
         </is>
       </c>
       <c r="C523" t="n">
@@ -8612,8 +8624,8 @@
       </c>
       <c r="B531" s="1" t="inlineStr">
         <is>
-          <t>「Aaaah… I'm coming… I'm cumming！ Ku, kuuuh！ Onii-chan…
-Onii！ Fwaaah！」</t>
+          <t>「Aaaah… I'm coming… I'm cumming！ Ku, kuuuh！
+Onii-chan… Onii！ Fwaaah！」</t>
         </is>
       </c>
       <c r="C531" t="n">
@@ -9042,8 +9054,8 @@
       </c>
       <c r="B559" s="1" t="inlineStr">
         <is>
-          <t>I was getting just as worked up in this situation, and
-the feeling was so good I couldn’t stop…！</t>
+          <t>I was getting just as worked up in this situation,
+and the feeling was so good I couldn’t stop…！</t>
         </is>
       </c>
       <c r="C559" t="n">
@@ -9243,8 +9255,8 @@
       </c>
       <c r="B572" s="1" t="inlineStr">
         <is>
-          <t>That Miru-chan is so precious that just the feeling of
-it makes my mind go completely blank.</t>
+          <t>That Miru-chan is so precious that just the feeling
+of it makes my mind go completely blank.</t>
         </is>
       </c>
       <c r="C572" t="n">
@@ -9335,8 +9347,9 @@
       </c>
       <c r="B578" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan reached her climax and her pussy trembled...
-and at the same time, I was pushed to orgasm too.</t>
+          <t>Miru-chan reached her climax and her pussy
+trembled... and at the same time, I was pushed to
+orgasm too.</t>
         </is>
       </c>
       <c r="C578" t="n">
@@ -9687,8 +9700,8 @@
       </c>
       <c r="B601" s="1" t="inlineStr">
         <is>
-          <t>「Fuh, eheh... it's still... it still feels good... ah,
-it feels good...」</t>
+          <t>「Fuh, eheh... it's still... it still feels good...
+ah, it feels good...」</t>
         </is>
       </c>
       <c r="C601" t="n">
@@ -9930,8 +9943,9 @@
       </c>
       <c r="B617" s="1" t="inlineStr">
         <is>
-          <t>…Somehow I managed to fix my clothes before the Ferris
-wheel door opened, but after that it was just chaos.</t>
+          <t>…Somehow I managed to fix my clothes before the
+Ferris wheel door opened, but after that it was just
+chaos.</t>
         </is>
       </c>
       <c r="C617" t="n">
@@ -10920,8 +10934,8 @@
       </c>
       <c r="B682" s="1" t="inlineStr">
         <is>
-          <t>When I deliberately spoke in our usual tone, Miru-chan
-went back to speaking in hers too.</t>
+          <t>When I deliberately spoke in our usual tone,
+Miru-chan went back to speaking in hers too.</t>
         </is>
       </c>
       <c r="C682" t="n">
@@ -10969,8 +10983,8 @@
       </c>
       <c r="B685" s="1" t="inlineStr">
         <is>
-          <t>Even so, Miru-chan stays the same Miru-chan she always
-is.</t>
+          <t>Even so, Miru-chan stays the same Miru-chan she
+always is.</t>
         </is>
       </c>
       <c r="C685" t="n">

--- a/processed_ruby_restored_xlsx/sc248_みるくＡ：遊園地.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc248_みるくＡ：遊園地.ss.xlsx
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>「Oh wow...！ You're doing it twice...！」</t>
+          <t>Oh wow...！ You're doing it twice...！</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>I noticed in her that special cuteness unique to
+          <t>I noticed in them that special cuteness unique to
 little kids and felt all warm and fuzzy.</t>
         </is>
       </c>
@@ -1957,8 +1957,8 @@
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>「Ugh！ I told you, I wouldn't do it in a place like
-this！」</t>
+          <t>Ugh！ I told you, I wouldn't do it in a place like
+this！</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2185,8 +2185,8 @@
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>「…Those people in the gondola over there…that
-couple…they're kissing, aren't they？」</t>
+          <t>…Those people in the gondola over there…that
+couple…they're kissing, aren't they？</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t>「slurrrp, sm…chuuuh…sputchuu, chuu…schlp, chuu…」</t>
+          <t>slurrrp, sm…chuuuh…sputchuu, chuu…schlp, chuu…</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3740,8 +3740,8 @@
       </c>
       <c r="B214" s="1" t="inlineStr">
         <is>
-          <t>「Mmm, mmm！ Smooch！ Smooch-puuu, chu, pwaa... smooch！
-Smooch！」</t>
+          <t>Mmm, mmm！ Smooch！ Smooch-puuu, chu, pwaa... smooch！
+Smooch！</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -4661,7 +4661,7 @@
       <c r="B274" s="1" t="inlineStr">
         <is>
           <t>Maybe she had been holding her breath the whole
-time...？</t>
+time...？"</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>I had her clothes pulled down to her waist and her
+          <t>He had her clothes pulled down to her waist and her
 underwear removed, and my head suddenly went hot.</t>
         </is>
       </c>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="B318" s="1" t="inlineStr">
         <is>
-          <t>「Nnaaahh！ Nn... nfu... nyan！ Nn！ Nn！ Nn...！」</t>
+          <t>Nnaaahh！ Nn... nfu... nyan！ Nn！ Nn！ Nn...！</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="B322" s="1" t="inlineStr">
         <is>
-          <t>「Nnh... nfu... nyah！ Nn, nn」</t>
+          <t>Nnh... nfu... nyah！ Nn, nn</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="B328" s="1" t="inlineStr">
         <is>
-          <t>「Y-yeah... that's an amazing sound, huh.」</t>
+          <t>Y-yeah... that's an amazing sound, huh.</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="B398" s="1" t="inlineStr">
         <is>
-          <t>「Hurry up... what do you want me to do？」</t>
+          <t>Hurry up... what do you want me to do？</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="B421" s="1" t="inlineStr">
         <is>
-          <t>「Uuuugh！ Ngh！ Fuuuu... Fuuuuh！ Ngh... Nngh！ Fwaaah！」</t>
+          <t>Uuuugh！ Ngh！ Fuuuu... Fuuuuh！ Ngh... Nngh！ Fwaaah！</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -7084,8 +7084,8 @@
       </c>
       <c r="B432" s="1" t="inlineStr">
         <is>
-          <t>「Nn, muuu... faaah... Onii-chan, after all, I
-can't... hold it... anymore...！」</t>
+          <t>Nn, muuu... faaah... Onii-chan, after all, I can't...
+hold it... anymore...！</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="B436" s="1" t="inlineStr">
         <is>
-          <t>「Heh... the person behind us might hear, you know？」</t>
+          <t>Heh... the person behind us might hear, you know？</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -7271,8 +7271,7 @@
       </c>
       <c r="B444" s="1" t="inlineStr">
         <is>
-          <t>「Nn, nnn~！ I can… I ca, nna！ Hah！ Haa… fu, faaa…
-nn~！」</t>
+          <t>Nn, nnn~！ I can… I ca, nna！ Hah！ Haa… fu, faaa… nn~！</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -7475,8 +7474,8 @@
       </c>
       <c r="B457" s="1" t="inlineStr">
         <is>
-          <t>She's already accepted the ensemble of splashing and
-gasps, and it seems she no longer notices it.</t>
+          <t>They've already accepted the ensemble of splashing
+and gasps, and it seems they no longer notice it.</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -7568,9 +7567,9 @@
       </c>
       <c r="B463" s="1" t="inlineStr">
         <is>
-          <t>When she says something different from what I was
-thinking, it makes her even more endearing and I
-start to find her really lovable.</t>
+          <t>When they say something different from what I was
+thinking, it makes them even more endearing and I
+start to find them really lovable.</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -7600,8 +7599,8 @@
       </c>
       <c r="B465" s="1" t="inlineStr">
         <is>
-          <t>「Huff... hnn... Your naughty juices are dripping,
-drip drip.」</t>
+          <t>Huff... hnn... Your naughty juices are dripping, drip
+drip.</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -7631,7 +7630,7 @@
       </c>
       <c r="B467" s="1" t="inlineStr">
         <is>
-          <t>「Huh？ Eh, nng？」</t>
+          <t>Huh？ Eh, nng？</t>
         </is>
       </c>
       <c r="C467" t="n">
@@ -7661,8 +7660,8 @@
       </c>
       <c r="B469" s="1" t="inlineStr">
         <is>
-          <t>「All warm and thick with love-juice... it's
-squelching... that sound is so filthy.」</t>
+          <t>All warm and thick with love-juice... it's
+squelching... that sound is so filthy.</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -8036,7 +8035,7 @@
       <c r="B493" s="1" t="inlineStr">
         <is>
           <t>Aaaahhh... why did I go and keep up this teasing
-play...！？</t>
+play...！？"</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -8220,7 +8219,7 @@
       </c>
       <c r="B505" s="1" t="inlineStr">
         <is>
-          <t>「Uhaa... then, let's do it all the way...！」</t>
+          <t>Uhaa... then, let's do it all the way...！</t>
         </is>
       </c>
       <c r="C505" t="n">
@@ -8250,7 +8249,7 @@
       </c>
       <c r="B507" s="1" t="inlineStr">
         <is>
-          <t>「Yeah... ah！ Ahh, ah！ Ha！」</t>
+          <t>Yeah... ah！ Ahh, ah！ Ha！</t>
         </is>
       </c>
       <c r="C507" t="n">
@@ -8343,8 +8342,8 @@
       </c>
       <c r="B513" s="1" t="inlineStr">
         <is>
-          <t>I slam my hips down with enough force to drown out
-that voice, and make one final sprint.</t>
+          <t>He slams his hips down with enough force to drown out
+that voice, and makes one final sprint.</t>
         </is>
       </c>
       <c r="C513" t="n">
@@ -8392,7 +8391,7 @@
         <is>
           <t>Miru-chan's getting frenzied and thrown off in the
 same way, down there feels all untied in a delicious
-way, and above all she's totally losing herself...</t>
+way, and above all she's totally losing herself..."</t>
         </is>
       </c>
       <c r="C516" t="n">
@@ -8438,8 +8437,8 @@
       </c>
       <c r="B519" s="1" t="inlineStr">
         <is>
-          <t>「Huh！ Huu—！ If the Ferris wheel keeps going down like
-this, the people waiting might see us, right？」</t>
+          <t>Huh！ Huu—！ If the Ferris wheel keeps going down like
+this, the people waiting might see us, right？</t>
         </is>
       </c>
       <c r="C519" t="n">
@@ -8592,7 +8591,7 @@
       </c>
       <c r="B529" s="1" t="inlineStr">
         <is>
-          <t>My penis swelled even bigger and harder inside, and
+          <t>Her penis swelled even bigger and harder inside, and
 waves of pleasure kept pouring out, driving the
 excitement even higher！</t>
         </is>
@@ -8852,7 +8851,7 @@
       <c r="B546" s="1" t="inlineStr">
         <is>
           <t>Miru-chan reached climax, her vagina trembling... and
-at the same time, incidentally, my penis also burst
+at the same time, incidentally, his penis also burst
 apart.</t>
         </is>
       </c>
@@ -8913,9 +8912,9 @@
       </c>
       <c r="B550" s="1" t="inlineStr">
         <is>
-          <t>Caught up by Miru-chan's climax, I reached my own...
-and with that momentum, my penis came out of her
-vagina.</t>
+          <t>Caught up by Miru-chan's climax, he reached his
+own... and with that momentum, his penis came out of
+her vagina.</t>
         </is>
       </c>
       <c r="C550" t="n">
@@ -9085,8 +9084,8 @@
       </c>
       <c r="B561" s="1" t="inlineStr">
         <is>
-          <t>「Noo… ah, noo…! It's still coming out… my butt…! It's
-so hot, it's on me…!」</t>
+          <t>Noo… ah, noo…! It's still coming out… my butt…! It's
+so hot, it's on me…!</t>
         </is>
       </c>
       <c r="C561" t="n">
@@ -9286,7 +9285,7 @@
       </c>
       <c r="B574" s="1" t="inlineStr">
         <is>
-          <t>「Aahhh！ I'm cumming！ Aahhh, ah！」</t>
+          <t>Aahhh！ I'm cumming！ Aahhh, ah！</t>
         </is>
       </c>
       <c r="C574" t="n">
@@ -9700,8 +9699,8 @@
       </c>
       <c r="B601" s="1" t="inlineStr">
         <is>
-          <t>「Fuh, eheh... it's still... it still feels good...
-ah, it feels good...」</t>
+          <t>Fuh, eheh... it's still... it still feels good... ah,
+it feels good...</t>
         </is>
       </c>
       <c r="C601" t="n">
@@ -10051,7 +10050,7 @@
       </c>
       <c r="B624" s="1" t="inlineStr">
         <is>
-          <t>「Haha, I don't think the ride's going anywhere...」</t>
+          <t>Haha, I don't think the ride's going anywhere...</t>
         </is>
       </c>
       <c r="C624" t="n">
